--- a/化学检验员理论复习资料20260918修订（505道）.xlsx
+++ b/化学检验员理论复习资料20260918修订（505道）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21423\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A045A40-FC4A-4A62-BAA7-6EDEC5D95E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39601B7D-CA82-4BAE-99D2-4997D863278D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="2071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="2072">
   <si>
     <t>A</t>
   </si>
@@ -15398,6 +15398,10 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>A,B,C</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -16148,7 +16152,7 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3" t="s">
-        <v>31</v>
+        <v>2071</v>
       </c>
       <c r="L5" s="1"/>
     </row>
